--- a/appium-tests/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/appium-tests/Test Results/Excel/Automation_Test_Report.xlsx
@@ -977,7 +977,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-09 14:02  |  Total Test Cases: 305  |  App: com.smartlearn.companion  |  Platform: Android (Appium UiAutomator2)</t>
+          <t>Generated: 2026-07-22 10:44  |  Total Test Cases: 305  |  App: com.smartlearn.companion  |  Platform: Android (Appium UiAutomator2)</t>
         </is>
       </c>
     </row>
